--- a/Result/profitability/3284.xlsx
+++ b/Result/profitability/3284.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.55375</v>
+        <v>0.4275</v>
       </c>
       <c r="N2" t="n">
-        <v>25.25875</v>
+        <v>23.6625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4062499999999999</v>
+        <v>0.4275</v>
       </c>
       <c r="N3" t="n">
-        <v>23.62875</v>
+        <v>23.19875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.40375</v>
+        <v>0.3612499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>23.1775</v>
+        <v>20.66125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.30875</v>
+        <v>0.32625</v>
       </c>
       <c r="N5" t="n">
-        <v>20.23875</v>
+        <v>19.0975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3225</v>
+        <v>0.27</v>
       </c>
       <c r="N6" t="n">
-        <v>19.24875</v>
+        <v>18.68625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.285</v>
+        <v>0.1724999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>19.32875</v>
+        <v>18.14875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19375</v>
+        <v>0.1587499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>18.98875</v>
+        <v>17.4875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,16 +1403,16 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>195</v>
+      </c>
+      <c r="D75" t="n">
+        <v>164</v>
+      </c>
+      <c r="E75" t="n">
+        <v>31</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.6475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.01</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4331049404976559</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3674044265593561</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
